--- a/output/yearly_surface_area_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_74_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449762127197</v>
+        <v>10.84497639938324</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907152553066</v>
+        <v>37.78907217595548</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.657812019574368</v>
+        <v>5.317145566200725</v>
       </c>
       <c r="C2" t="n">
-        <v>6.289075793405067</v>
+        <v>6.120215188274616</v>
       </c>
       <c r="D2" t="n">
-        <v>34.17365583712722</v>
+        <v>36.51708760716436</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.60840583919254</v>
+        <v>15.90922154731956</v>
       </c>
       <c r="C3" t="n">
-        <v>28.44613973055133</v>
+        <v>28.76029899591031</v>
       </c>
       <c r="D3" t="n">
-        <v>77.9311327631118</v>
+        <v>80.22351365252811</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.01264921363074</v>
+        <v>34.089225534562</v>
       </c>
       <c r="C4" t="n">
-        <v>85.31878423756905</v>
+        <v>59.57637768451344</v>
       </c>
       <c r="D4" t="n">
-        <v>91.13858462834415</v>
+        <v>112.1460220038174</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.1541029985003</v>
+        <v>42.55876297909924</v>
       </c>
       <c r="C5" t="n">
-        <v>134.204911170539</v>
+        <v>90.63985679458678</v>
       </c>
       <c r="D5" t="n">
-        <v>61.92373644536757</v>
+        <v>87.8173321448772</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.08435785376978</v>
+        <v>40.97618567985338</v>
       </c>
       <c r="C6" t="n">
-        <v>137.7814180571101</v>
+        <v>105.0970734873253</v>
       </c>
       <c r="D6" t="n">
-        <v>42.9082651618111</v>
+        <v>55.38627848278806</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.76931465169778</v>
+        <v>29.76364514965055</v>
       </c>
       <c r="C7" t="n">
-        <v>101.2682574407627</v>
+        <v>104.9213406482651</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62686342359076</v>
+        <v>41.74096714146164</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>15.35453409442011</v>
       </c>
       <c r="C8" t="n">
-        <v>55.82708320199487</v>
+        <v>77.02301613668349</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>45.5953086283346</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.85071759569225</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.698371597172877</v>
+        <v>7.667052537053424</v>
       </c>
       <c r="C21" t="n">
-        <v>95.26734851501436</v>
+        <v>93.92139357890444</v>
       </c>
       <c r="D21" t="n">
-        <v>8.660668046819486</v>
+        <v>7.667052537053424</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.461863389352506</v>
+        <v>6.810383824360123</v>
       </c>
       <c r="C2" t="n">
-        <v>8.244717220264713</v>
+        <v>7.940375431948202</v>
       </c>
       <c r="D2" t="n">
-        <v>30.66390779444488</v>
+        <v>30.35171202449439</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.6209886328985</v>
+        <v>16.71425466480195</v>
       </c>
       <c r="C3" t="n">
-        <v>26.50227927614264</v>
+        <v>26.07521902479529</v>
       </c>
       <c r="D3" t="n">
-        <v>85.33351045313276</v>
+        <v>88.74999246391167</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.64329109265569</v>
+        <v>31.86851222755571</v>
       </c>
       <c r="C4" t="n">
-        <v>77.38037230102935</v>
+        <v>64.91119470939061</v>
       </c>
       <c r="D4" t="n">
-        <v>106.5559505758361</v>
+        <v>124.4748096737489</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.17297718905925</v>
+        <v>46.31394794784328</v>
       </c>
       <c r="C5" t="n">
-        <v>143.8751260573701</v>
+        <v>99.77011044408214</v>
       </c>
       <c r="D5" t="n">
-        <v>76.84630154991909</v>
+        <v>103.9179944945249</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.82525857530663</v>
+        <v>48.98626519880311</v>
       </c>
       <c r="C6" t="n">
-        <v>173.5651401292021</v>
+        <v>122.2845305455742</v>
       </c>
       <c r="D6" t="n">
-        <v>51.32086123950202</v>
+        <v>68.2265567066321</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.69241953559704</v>
+        <v>38.38731698375453</v>
       </c>
       <c r="C7" t="n">
-        <v>145.9436684702181</v>
+        <v>126.4805202335251</v>
       </c>
       <c r="D7" t="n">
-        <v>41.50142070162541</v>
+        <v>46.83132898798135</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.11248437982766</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="C8" t="n">
-        <v>92.54444734082557</v>
+        <v>106.814150222053</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>11.31562403914873</v>
       </c>
       <c r="C9" t="n">
-        <v>49.58905828921062</v>
+        <v>68.44843168779184</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>34.59188035913637</v>
+        <v>42.13661146627311</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
         <v>32.26022956155019</v>
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.85071759569225</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.87701303760035</v>
+        <v>7.845077323661437</v>
       </c>
       <c r="C21" t="n">
-        <v>103.3857961185046</v>
+        <v>101.9860052075987</v>
       </c>
       <c r="D21" t="n">
-        <v>9.846266297000438</v>
+        <v>8.825711989119116</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.6487963637869</v>
+        <v>7.123561342014856</v>
       </c>
       <c r="C2" t="n">
-        <v>9.557313900842699</v>
+        <v>15.45467236025329</v>
       </c>
       <c r="D2" t="n">
-        <v>30.5951854551476</v>
+        <v>30.07584091960104</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.74156367407161</v>
+        <v>19.17844140246144</v>
       </c>
       <c r="C3" t="n">
-        <v>28.82902133520759</v>
+        <v>28.05834938737384</v>
       </c>
       <c r="D3" t="n">
-        <v>88.02840790129025</v>
+        <v>90.6300393175443</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.32422308877548</v>
+        <v>31.16656261901924</v>
       </c>
       <c r="C4" t="n">
-        <v>71.35636838777093</v>
+        <v>64.18371966054373</v>
       </c>
       <c r="D4" t="n">
-        <v>118.8975009659227</v>
+        <v>134.7870875591573</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.38757902566179</v>
+        <v>47.1238898038469</v>
       </c>
       <c r="C5" t="n">
-        <v>142.9424657383356</v>
+        <v>107.3050240741764</v>
       </c>
       <c r="D5" t="n">
-        <v>92.94696389956678</v>
+        <v>120.2640937702343</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.78250364467628</v>
+        <v>54.42023874180921</v>
       </c>
       <c r="C6" t="n">
-        <v>195.462040924723</v>
+        <v>138.2241862717254</v>
       </c>
       <c r="D6" t="n">
-        <v>60.17622553180826</v>
+        <v>80.38255678061611</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.91495746929157</v>
+        <v>46.65166915810418</v>
       </c>
       <c r="C7" t="n">
-        <v>189.5411205204104</v>
+        <v>147.4408337191945</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>53.35896947351839</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.37250865273282</v>
+        <v>30.70906818884022</v>
       </c>
       <c r="C8" t="n">
-        <v>135.9376958685346</v>
+        <v>133.9349305518711</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.19843620944487</v>
+        <v>16.19687362466387</v>
       </c>
       <c r="C9" t="n">
-        <v>76.32499351896399</v>
+        <v>95.07342942696533</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>44.69897297435728</v>
+        <v>58.2225476003571</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>39.44858625204532</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.85071759569225</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.039360629900671</v>
+        <v>8.008309201457923</v>
       </c>
       <c r="C21" t="n">
-        <v>111.5461287398718</v>
+        <v>110.1142515200465</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05412086611342</v>
+        <v>10.0103865018224</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.956664232292898</v>
+        <v>6.557092916664446</v>
       </c>
       <c r="C2" t="n">
-        <v>6.574764375340889</v>
+        <v>10.50862742625786</v>
       </c>
       <c r="D2" t="n">
-        <v>25.32025504022949</v>
+        <v>24.9305012016435</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.75062038758809</v>
+        <v>22.3003991019663</v>
       </c>
       <c r="C3" t="n">
-        <v>44.35536127787089</v>
+        <v>46.39739650270426</v>
       </c>
       <c r="D3" t="n">
-        <v>94.32631942403354</v>
+        <v>98.57728698342224</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.2837093909941</v>
+        <v>22.64106555533994</v>
       </c>
       <c r="C4" t="n">
-        <v>110.3975293425538</v>
+        <v>88.6753796383889</v>
       </c>
       <c r="D4" t="n">
-        <v>111.022902630159</v>
+        <v>131.2135259156989</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.85142160595602</v>
+        <v>30.65507206510666</v>
       </c>
       <c r="C5" t="n">
-        <v>116.7788894201581</v>
+        <v>82.58952561976294</v>
       </c>
       <c r="D5" t="n">
-        <v>60.94198874112077</v>
+        <v>80.35604959260144</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.89439752076462</v>
+        <v>28.94094057349173</v>
       </c>
       <c r="C6" t="n">
-        <v>124.8203848656437</v>
+        <v>97.08699396837559</v>
       </c>
       <c r="D6" t="n">
-        <v>30.14849024971531</v>
+        <v>35.13969557810609</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.80439552714341</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C7" t="n">
-        <v>95.57902949465246</v>
+        <v>94.14175085563514</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>56.24432597629976</v>
+        <v>70.01333752836128</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>44.37499623195582</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
         <v>26.4698816019025</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
         <v>14.44641746799181</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.163592013710723</v>
+        <v>3.965278977452867</v>
       </c>
       <c r="C2" t="n">
-        <v>3.802308858547897</v>
+        <v>5.071708640139023</v>
       </c>
       <c r="D2" t="n">
-        <v>17.99838066195677</v>
+        <v>17.56248468127119</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.36068662255285</v>
+        <v>23.02689240310894</v>
       </c>
       <c r="C3" t="n">
-        <v>35.55399310929824</v>
+        <v>44.59588946541136</v>
       </c>
       <c r="D3" t="n">
-        <v>94.18396600691776</v>
+        <v>97.3893722612836</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.61776565234527</v>
+        <v>31.2559016601057</v>
       </c>
       <c r="C4" t="n">
-        <v>113.5499212208903</v>
+        <v>104.105508306036</v>
       </c>
       <c r="D4" t="n">
-        <v>128.035608597052</v>
+        <v>146.4905019414836</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.91938318172731</v>
+        <v>33.89483948912113</v>
       </c>
       <c r="C5" t="n">
-        <v>159.3867397844697</v>
+        <v>121.1231230114503</v>
       </c>
       <c r="D5" t="n">
-        <v>79.27612711792995</v>
+        <v>100.899120303966</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.12711278440013</v>
+        <v>34.13340418125311</v>
       </c>
       <c r="C6" t="n">
-        <v>155.4518949858485</v>
+        <v>116.2467821644563</v>
       </c>
       <c r="D6" t="n">
-        <v>37.35353665118265</v>
+        <v>45.00135126726531</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.78632315783946</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="C7" t="n">
-        <v>126.8398398932794</v>
+        <v>114.7427446815502</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>32.33876937788993</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>77.60715602071035</v>
+        <v>90.95892479846698</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>38.82812170296133</v>
+        <v>49.25624581747095</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>29.75186417719959</v>
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
         <v>12.27773678931061</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.764020698082271</v>
+        <v>3.963315482044373</v>
       </c>
       <c r="C2" t="n">
-        <v>6.805475085838889</v>
+        <v>5.948409340031424</v>
       </c>
       <c r="D2" t="n">
-        <v>14.15091140901352</v>
+        <v>18.65615162380214</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.73665493555038</v>
+        <v>18.2359636063845</v>
       </c>
       <c r="C3" t="n">
-        <v>24.47987900539422</v>
+        <v>31.52391878336508</v>
       </c>
       <c r="D3" t="n">
-        <v>87.28227964606268</v>
+        <v>89.54029936583034</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.3820073346058</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C4" t="n">
-        <v>100.8510146664578</v>
+        <v>107.7301208301152</v>
       </c>
       <c r="D4" t="n">
-        <v>143.210482861595</v>
+        <v>159.4446628990202</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.41717032550945</v>
+        <v>40.00621894805753</v>
       </c>
       <c r="C5" t="n">
-        <v>185.3294228691917</v>
+        <v>156.9569142164588</v>
       </c>
       <c r="D5" t="n">
-        <v>102.494460323367</v>
+        <v>125.5900750657732</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.80259626265094</v>
+        <v>39.92964262712628</v>
       </c>
       <c r="C6" t="n">
-        <v>200.7350078442326</v>
+        <v>151.5072327101848</v>
       </c>
       <c r="D6" t="n">
-        <v>50.19381487502668</v>
+        <v>61.7460401108989</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.35010838198439</v>
+        <v>27.60772719112455</v>
       </c>
       <c r="C7" t="n">
-        <v>173.0124161717111</v>
+        <v>140.9131932336574</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>118.1631536831461</v>
+        <v>119.4983305609218</v>
       </c>
       <c r="D8" t="n">
         <v>30.0414797499524</v>
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>63.12343213995715</v>
+        <v>76.32499351896399</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>38.15071578703105</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.05273663858884</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.87936820556466</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
         <v>11.33329549782518</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.270782439922872</v>
+        <v>2.359139733305085</v>
       </c>
       <c r="C2" t="n">
-        <v>3.173990327829938</v>
+        <v>2.796017461694916</v>
       </c>
       <c r="D2" t="n">
-        <v>9.893071615695108</v>
+        <v>13.02190154912969</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.10342766631118</v>
+        <v>18.11324514335365</v>
       </c>
       <c r="C3" t="n">
-        <v>26.93915700453248</v>
+        <v>29.96293993361266</v>
       </c>
       <c r="D3" t="n">
-        <v>83.60563449365839</v>
+        <v>87.92041565382311</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.21082338116835</v>
+        <v>40.73860273542564</v>
       </c>
       <c r="C4" t="n">
-        <v>97.25192758268904</v>
+        <v>107.411052826235</v>
       </c>
       <c r="D4" t="n">
-        <v>153.4717098663826</v>
+        <v>169.2081438177547</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.01251034491051</v>
+        <v>42.16606389740051</v>
       </c>
       <c r="C5" t="n">
-        <v>215.2972715413256</v>
+        <v>192.3243752619502</v>
       </c>
       <c r="D5" t="n">
-        <v>108.6303834749096</v>
+        <v>132.2414157620454</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.12082138754715</v>
+        <v>33.36862271964485</v>
       </c>
       <c r="C6" t="n">
-        <v>237.0822530985623</v>
+        <v>181.615471304026</v>
       </c>
       <c r="D6" t="n">
-        <v>49.30827844579606</v>
+        <v>59.89446394068941</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.26435217434965</v>
+        <v>9.042878103817369</v>
       </c>
       <c r="C7" t="n">
-        <v>170.9163848231442</v>
+        <v>151.8724428561646</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07548106670254</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>82.36372364778616</v>
+        <v>92.54444734082557</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>29.06562253193106</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
         <v>31.50624732468863</v>
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>11.82515109765283</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.541826921753</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
         <v>9.506263020221864</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.494620916491145</v>
+        <v>2.661518026213103</v>
       </c>
       <c r="C2" t="n">
-        <v>4.193044444838127</v>
+        <v>5.502695882303372</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8345676640678</v>
+        <v>17.50750680983337</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.13087554430109</v>
+        <v>13.27813769993811</v>
       </c>
       <c r="C3" t="n">
-        <v>19.53677931451153</v>
+        <v>20.25836387713293</v>
       </c>
       <c r="D3" t="n">
-        <v>74.14649536324036</v>
+        <v>79.75227475448963</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.45407582764332</v>
+        <v>38.19882142453914</v>
       </c>
       <c r="C4" t="n">
-        <v>83.35332533366693</v>
+        <v>92.32551760277855</v>
       </c>
       <c r="D4" t="n">
-        <v>158.6150860889317</v>
+        <v>173.1773497860246</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.7746086053133</v>
+        <v>50.24093876483053</v>
       </c>
       <c r="C5" t="n">
-        <v>200.3992501293802</v>
+        <v>194.606938674324</v>
       </c>
       <c r="D5" t="n">
-        <v>132.1677846842269</v>
+        <v>156.0242538974244</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.89568236810514</v>
+        <v>42.30449032369931</v>
       </c>
       <c r="C6" t="n">
-        <v>285.1427302122607</v>
+        <v>239.9803723214989</v>
       </c>
       <c r="D6" t="n">
-        <v>65.97246397768143</v>
+        <v>80.18129850124551</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>245.4153276122092</v>
+        <v>199.6619576034908</v>
       </c>
       <c r="D7" t="n">
-        <v>39.04606969330414</v>
+        <v>42.93869934064274</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>138.8583952886689</v>
+        <v>137.4397698560322</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>55.02499532762521</v>
+        <v>63.34530712111692</v>
       </c>
       <c r="D9" t="n">
         <v>32.39374724932775</v>
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
         <v>23.63361248433346</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.873174619702914</v>
+        <v>1.876119862815655</v>
       </c>
       <c r="C2" t="n">
-        <v>2.701769682087222</v>
+        <v>3.059125846433061</v>
       </c>
       <c r="D2" t="n">
-        <v>8.757189521881548</v>
+        <v>12.84322346695677</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.31955102996572</v>
+        <v>11.64352777236717</v>
       </c>
       <c r="C3" t="n">
-        <v>18.25559856046944</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D3" t="n">
-        <v>68.42781498600269</v>
+        <v>76.3456102207532</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.28066633689012</v>
+        <v>34.20409001595887</v>
       </c>
       <c r="C4" t="n">
-        <v>70.8841477420282</v>
+        <v>77.07406701730434</v>
       </c>
       <c r="D4" t="n">
-        <v>159.5722901005723</v>
+        <v>175.8192328581528</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.3151917374548</v>
+        <v>54.14338588921161</v>
       </c>
       <c r="C5" t="n">
-        <v>189.6736564604838</v>
+        <v>190.0908992347887</v>
       </c>
       <c r="D5" t="n">
-        <v>147.6548547187203</v>
+        <v>171.4622365467055</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.69821221083129</v>
+        <v>49.91205328390785</v>
       </c>
       <c r="C6" t="n">
-        <v>310.1792601659628</v>
+        <v>276.7703857904439</v>
       </c>
       <c r="D6" t="n">
-        <v>80.14104684537139</v>
+        <v>96.72472906550851</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.16938468894497</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C7" t="n">
-        <v>304.1640919820425</v>
+        <v>248.2898848902438</v>
       </c>
       <c r="D7" t="n">
-        <v>43.35790561035613</v>
+        <v>48.20872101703962</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>182.9192322552657</v>
+        <v>175.2419652080556</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>63.34530712111692</v>
+        <v>71.44374393344886</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3400,7 +3400,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3414,7 +3414,7 @@
         <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.905973204570559</v>
+        <v>3.192643534210627</v>
       </c>
       <c r="C2" t="n">
-        <v>12.22275891787279</v>
+        <v>13.14069302134356</v>
       </c>
       <c r="D2" t="n">
-        <v>11.28813510342983</v>
+        <v>10.76879056788326</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.963356539773379</v>
+        <v>9.144979865059039</v>
       </c>
       <c r="C3" t="n">
-        <v>14.56913593102267</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D3" t="n">
-        <v>61.08925089675778</v>
+        <v>70.00352005131882</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.33323874456295</v>
+        <v>28.55020498720149</v>
       </c>
       <c r="C4" t="n">
-        <v>59.5125640837374</v>
+        <v>65.9322123218073</v>
       </c>
       <c r="D4" t="n">
-        <v>157.351576793566</v>
+        <v>173.7389094728538</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.16163818496479</v>
+        <v>52.98983233672161</v>
       </c>
       <c r="C5" t="n">
-        <v>164.197303535279</v>
+        <v>169.2533042121501</v>
       </c>
       <c r="D5" t="n">
-        <v>164.5409152317654</v>
+        <v>188.6428213710246</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.23785465299754</v>
+        <v>58.6064109527176</v>
       </c>
       <c r="C6" t="n">
-        <v>307.884915781138</v>
+        <v>287.8395911558266</v>
       </c>
       <c r="D6" t="n">
-        <v>99.30083504145215</v>
+        <v>118.500874893407</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.52409870981433</v>
+        <v>31.08115056874977</v>
       </c>
       <c r="C7" t="n">
-        <v>365.6077538000334</v>
+        <v>311.4702583970473</v>
       </c>
       <c r="D7" t="n">
-        <v>51.80191761458295</v>
+        <v>58.92842419971054</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>265.4498530127738</v>
+        <v>233.6559536107408</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>122.0312396378785</v>
+        <v>124.2499894494763</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>45.98015372839937</v>
+        <v>49.96604940764142</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.36962016288231</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.840997929641022</v>
+        <v>5.89441321629785</v>
       </c>
       <c r="C2" t="n">
-        <v>3.352668410002857</v>
+        <v>9.376672323261285</v>
       </c>
       <c r="D2" t="n">
-        <v>6.567892141411161</v>
+        <v>19.2697439389564</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.101921834792421</v>
+        <v>2.309070600388498</v>
       </c>
       <c r="C2" t="n">
-        <v>7.040112787153877</v>
+        <v>7.568293052038661</v>
       </c>
       <c r="D2" t="n">
-        <v>8.397869862127216</v>
+        <v>7.926630964088747</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.3258424268187</v>
+        <v>12.62036673809275</v>
       </c>
       <c r="C3" t="n">
-        <v>26.27647730416588</v>
+        <v>29.09900195387546</v>
       </c>
       <c r="D3" t="n">
-        <v>65.87036221643974</v>
+        <v>75.13806054452964</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.99836496642355</v>
+        <v>40.02389040673396</v>
       </c>
       <c r="C4" t="n">
-        <v>87.80751466783472</v>
+        <v>95.32475683925254</v>
       </c>
       <c r="D4" t="n">
-        <v>161.0144774781109</v>
+        <v>178.6525567326091</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.20761609614836</v>
+        <v>33.99301425954582</v>
       </c>
       <c r="C5" t="n">
-        <v>254.6162670964103</v>
+        <v>246.4432174585556</v>
       </c>
       <c r="D5" t="n">
-        <v>148.1211848782375</v>
+        <v>171.2167996206437</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.31450342272425</v>
+        <v>19.28054316370311</v>
       </c>
       <c r="C6" t="n">
-        <v>298.1440150596011</v>
+        <v>261.5552598700268</v>
       </c>
       <c r="D6" t="n">
-        <v>78.32972233103602</v>
+        <v>91.81402704886597</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>186.6665632423758</v>
+        <v>164.3288577276481</v>
       </c>
       <c r="D7" t="n">
-        <v>32.45854259780804</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>89.95754214013523</v>
+        <v>91.54306468249383</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>35.05624702324509</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
         <v>9.365873098514571</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.356816384998097</v>
+        <v>7.074473956802516</v>
       </c>
       <c r="C2" t="n">
-        <v>5.811946409141117</v>
+        <v>5.133558745506572</v>
       </c>
       <c r="D2" t="n">
-        <v>11.98419422574081</v>
+        <v>23.03081939392592</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.28871594050657</v>
+        <v>12.52219196766807</v>
       </c>
       <c r="C3" t="n">
-        <v>8.580474935117122</v>
+        <v>23.62575850269949</v>
       </c>
       <c r="D3" t="n">
-        <v>8.914269154561039</v>
+        <v>19.32079481957723</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39947031287173</v>
+        <v>13.39607697240599</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15016810856376</v>
+        <v>70.13240297318431</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576408272102556</v>
+        <v>1.576009055577176</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.867104207028186</v>
+        <v>4.734969177582366</v>
       </c>
       <c r="C2" t="n">
-        <v>6.450082416901544</v>
+        <v>3.564725914120168</v>
       </c>
       <c r="D2" t="n">
-        <v>17.31115726898401</v>
+        <v>24.55645532632547</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5143790437631</v>
+        <v>19.65949777754238</v>
       </c>
       <c r="C3" t="n">
-        <v>17.53892273636927</v>
+        <v>21.36773878293183</v>
       </c>
       <c r="D3" t="n">
-        <v>16.82715565079033</v>
+        <v>33.99792299806705</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.04800782651686</v>
+        <v>14.57502641724815</v>
       </c>
       <c r="C4" t="n">
-        <v>13.83478864824605</v>
+        <v>36.55243052451725</v>
       </c>
       <c r="D4" t="n">
-        <v>19.7439280801076</v>
+        <v>25.19360958638165</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.58368222013712</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4460574726875</v>
+        <v>15.43495119701179</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1727416897303</v>
+        <v>86.11078036227633</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25180157319737</v>
+        <v>3.24946340989722</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.776202581160732</v>
+        <v>4.82921695719006</v>
       </c>
       <c r="C2" t="n">
-        <v>11.5728419376614</v>
+        <v>5.732424845097126</v>
       </c>
       <c r="D2" t="n">
-        <v>19.42191483311465</v>
+        <v>34.60366133158733</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.19254572321939</v>
+        <v>17.81872083207961</v>
       </c>
       <c r="C3" t="n">
-        <v>22.37893891830604</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D3" t="n">
-        <v>26.76735115628928</v>
+        <v>45.7543517564226</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.73415166079414</v>
+        <v>27.91206897944107</v>
       </c>
       <c r="C4" t="n">
-        <v>31.396291581813</v>
+        <v>46.02236887968198</v>
       </c>
       <c r="D4" t="n">
-        <v>23.55998140651495</v>
+        <v>36.55243052451725</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.99557428756428</v>
+        <v>12.73817646260237</v>
       </c>
       <c r="C5" t="n">
-        <v>17.0824100538945</v>
+        <v>40.84070449666732</v>
       </c>
       <c r="D5" t="n">
-        <v>29.91876128692155</v>
+        <v>31.68590715456581</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.39751000922872</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.2069942013426</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.82722207071512</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74584644456067</v>
+        <v>16.722715668255</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1496633118201</v>
+        <v>102.0085655763555</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023753933368201</v>
+        <v>4.180678917063751</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.221335201812037</v>
+        <v>5.120796025351362</v>
       </c>
       <c r="C2" t="n">
-        <v>7.38372448364026</v>
+        <v>5.462444226429254</v>
       </c>
       <c r="D2" t="n">
-        <v>31.77033745713103</v>
+        <v>30.39294542807275</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.83559046950105</v>
+        <v>17.0824100538945</v>
       </c>
       <c r="C3" t="n">
-        <v>35.62271544859551</v>
+        <v>19.90002596508285</v>
       </c>
       <c r="D3" t="n">
-        <v>35.57362806338318</v>
+        <v>61.87464906015522</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.18459393059418</v>
+        <v>31.23037621979529</v>
       </c>
       <c r="C4" t="n">
-        <v>45.39699559207676</v>
+        <v>43.49535028895069</v>
       </c>
       <c r="D4" t="n">
-        <v>31.01340997715674</v>
+        <v>50.46379549369455</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.32279937271473</v>
+        <v>27.26804248545517</v>
       </c>
       <c r="C5" t="n">
-        <v>39.56443248114646</v>
+        <v>64.69717370986481</v>
       </c>
       <c r="D5" t="n">
-        <v>31.80862561759666</v>
+        <v>37.08551952792327</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.42517887139688</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C6" t="n">
-        <v>19.96482131356314</v>
+        <v>39.48687441251096</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>38.68184129502858</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
         <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.40016181936776</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07998470944377</v>
+        <v>18.03938146227341</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9503764377998</v>
+        <v>117.6854885872122</v>
       </c>
       <c r="D21" t="n">
-        <v>6.887613222645246</v>
+        <v>6.013127154091136</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.183047041346412</v>
+        <v>5.998478472948011</v>
       </c>
       <c r="C2" t="n">
-        <v>10.85125737504</v>
+        <v>7.933503198018475</v>
       </c>
       <c r="D2" t="n">
-        <v>30.69630546868502</v>
+        <v>26.90970457340507</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.97932654494859</v>
+        <v>15.55088363526948</v>
       </c>
       <c r="C3" t="n">
-        <v>29.71259426902972</v>
+        <v>19.35515598922587</v>
       </c>
       <c r="D3" t="n">
-        <v>48.73395603881167</v>
+        <v>66.99446333780234</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.35203081966388</v>
+        <v>23.18986252201391</v>
       </c>
       <c r="C4" t="n">
-        <v>58.96376711706343</v>
+        <v>38.90077103307561</v>
       </c>
       <c r="D4" t="n">
-        <v>35.76114187489431</v>
+        <v>60.27832729304991</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.00310947402876</v>
+        <v>22.58019719767664</v>
       </c>
       <c r="C5" t="n">
-        <v>47.41841411512095</v>
+        <v>54.3151917374548</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>37.20823799095412</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.99499345048753</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>28.53842401475054</v>
+        <v>48.74475526355839</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>32.28182801104362</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>16.28915790886308</v>
+        <v>24.852943133008</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.63281066307846</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.068651193289663</v>
+        <v>7.047245906990762</v>
       </c>
       <c r="C21" t="n">
-        <v>67.15218633625179</v>
+        <v>66.0679303780384</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301488394967246</v>
+        <v>4.404528691869226</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.603414985213294</v>
+        <v>5.10017932356218</v>
       </c>
       <c r="C2" t="n">
-        <v>8.494081137143404</v>
+        <v>5.917975161199774</v>
       </c>
       <c r="D2" t="n">
-        <v>31.46501392111027</v>
+        <v>23.67680938332033</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.90493470360408</v>
+        <v>18.83482970597506</v>
       </c>
       <c r="C3" t="n">
-        <v>38.04763227808514</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D3" t="n">
-        <v>63.50435024920493</v>
+        <v>73.41018458505525</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.84374755077129</v>
+        <v>27.59300097556086</v>
       </c>
       <c r="C4" t="n">
-        <v>68.96973971874692</v>
+        <v>44.98858854711009</v>
       </c>
       <c r="D4" t="n">
-        <v>53.87144177513522</v>
+        <v>80.82630674293564</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.0716929446058</v>
+        <v>30.01693605734623</v>
       </c>
       <c r="C5" t="n">
-        <v>85.68203088814039</v>
+        <v>65.16350386938205</v>
       </c>
       <c r="D5" t="n">
-        <v>36.20194659410114</v>
+        <v>51.93445355465628</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.89060939866788</v>
+        <v>23.2252054393668</v>
       </c>
       <c r="C6" t="n">
-        <v>56.51332484726341</v>
+        <v>70.96366930607222</v>
       </c>
       <c r="D6" t="n">
-        <v>32.96610616090365</v>
+        <v>37.31328499530853</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.4801567428347</v>
+        <v>11.25868267230242</v>
       </c>
       <c r="C7" t="n">
-        <v>31.14103717870882</v>
+        <v>51.44259795482861</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>20.77869016038374</v>
+        <v>27.20422888467911</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,10 +6224,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.292918793304072</v>
+        <v>7.26665558019207</v>
       </c>
       <c r="C21" t="n">
-        <v>76.57564732969276</v>
+        <v>75.39155164449274</v>
       </c>
       <c r="D21" t="n">
-        <v>6.381303944141063</v>
+        <v>5.449991685144053</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.517602024316322</v>
+        <v>4.107632394568655</v>
       </c>
       <c r="C2" t="n">
-        <v>6.012222940807467</v>
+        <v>8.295768100885548</v>
       </c>
       <c r="D2" t="n">
-        <v>27.40254192093697</v>
+        <v>29.07642175667778</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.67145867644259</v>
+        <v>18.17705874412969</v>
       </c>
       <c r="C3" t="n">
-        <v>35.01894061048372</v>
+        <v>24.55841882173396</v>
       </c>
       <c r="D3" t="n">
-        <v>73.94032834534852</v>
+        <v>75.31968386981529</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.3827680981318</v>
+        <v>32.9022925601276</v>
       </c>
       <c r="C4" t="n">
-        <v>84.48920742748051</v>
+        <v>57.45776613874882</v>
       </c>
       <c r="D4" t="n">
-        <v>73.5898444149324</v>
+        <v>99.48540360985054</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.17740290149497</v>
+        <v>36.20194659410114</v>
       </c>
       <c r="C5" t="n">
-        <v>109.5875874865502</v>
+        <v>75.47185476397355</v>
       </c>
       <c r="D5" t="n">
-        <v>47.02571503342222</v>
+        <v>68.72233929727673</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.46421209985528</v>
+        <v>32.92585450502953</v>
       </c>
       <c r="C6" t="n">
-        <v>99.66309994431923</v>
+        <v>89.07691444942586</v>
       </c>
       <c r="D6" t="n">
-        <v>37.31328499530853</v>
+        <v>45.48437113775474</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.38518925743002</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="C7" t="n">
-        <v>59.10808402958771</v>
+        <v>79.52941802562562</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>37.06981156465531</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>32.29459073119883</v>
+        <v>49.15119881311656</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.4046853427947</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.85071759569225</v>
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.503213679007269</v>
+        <v>7.473928959923118</v>
       </c>
       <c r="C21" t="n">
-        <v>86.2869573085836</v>
+        <v>85.01594191912547</v>
       </c>
       <c r="D21" t="n">
-        <v>7.503213679007269</v>
+        <v>6.539687839932729</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_74_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497639938324</v>
+        <v>10.84497625442496</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907217595548</v>
+        <v>37.78907167085168</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.317145566200725</v>
+        <v>8.784678457600458</v>
       </c>
       <c r="C2" t="n">
-        <v>6.120215188274616</v>
+        <v>8.161268665403735</v>
       </c>
       <c r="D2" t="n">
-        <v>36.51708760716436</v>
+        <v>16.21552683104457</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.90922154731956</v>
+        <v>21.50518346152638</v>
       </c>
       <c r="C3" t="n">
-        <v>28.76029899591031</v>
+        <v>27.94544840138546</v>
       </c>
       <c r="D3" t="n">
-        <v>80.22351365252811</v>
+        <v>61.4672237628928</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.089225534562</v>
+        <v>41.61923042613503</v>
       </c>
       <c r="C4" t="n">
-        <v>59.57637768451344</v>
+        <v>54.82864578677587</v>
       </c>
       <c r="D4" t="n">
-        <v>112.1460220038174</v>
+        <v>83.50647797552944</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.55876297909924</v>
+        <v>49.57825906446394</v>
       </c>
       <c r="C5" t="n">
-        <v>90.63985679458678</v>
+        <v>79.71791358484101</v>
       </c>
       <c r="D5" t="n">
-        <v>87.8173321448772</v>
+        <v>58.53670686571608</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.97618567985338</v>
+        <v>50.75733805726436</v>
       </c>
       <c r="C6" t="n">
-        <v>105.0970734873253</v>
+        <v>97.93227874173209</v>
       </c>
       <c r="D6" t="n">
-        <v>55.38627848278806</v>
+        <v>42.34474197957343</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.76364514965055</v>
+        <v>38.86640986342697</v>
       </c>
       <c r="C7" t="n">
-        <v>104.9213406482651</v>
+        <v>89.23104883899259</v>
       </c>
       <c r="D7" t="n">
-        <v>41.74096714146164</v>
+        <v>37.54890444432775</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>20.69524160552276</v>
       </c>
       <c r="C8" t="n">
-        <v>77.02301613668349</v>
+        <v>62.16917337142927</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>8.985936736971052</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>38.82812170296133</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.667052537053424</v>
+        <v>7.704944597242512</v>
       </c>
       <c r="C21" t="n">
-        <v>93.92139357890444</v>
+        <v>95.34868939087609</v>
       </c>
       <c r="D21" t="n">
-        <v>7.667052537053424</v>
+        <v>8.668062671897825</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.810383824360123</v>
+        <v>9.033060626774903</v>
       </c>
       <c r="C2" t="n">
-        <v>7.940375431948202</v>
+        <v>12.14912784005428</v>
       </c>
       <c r="D2" t="n">
-        <v>30.35171202449439</v>
+        <v>22.37501192748906</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.71425466480195</v>
+        <v>25.54998400302324</v>
       </c>
       <c r="C3" t="n">
-        <v>26.07521902479529</v>
+        <v>29.85003894762427</v>
       </c>
       <c r="D3" t="n">
-        <v>88.74999246391167</v>
+        <v>60.05841580729863</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.86851222755571</v>
+        <v>41.04490801915065</v>
       </c>
       <c r="C4" t="n">
-        <v>64.91119470939061</v>
+        <v>62.58837964114265</v>
       </c>
       <c r="D4" t="n">
-        <v>124.4748096737489</v>
+        <v>94.15058658497337</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.31394794784328</v>
+        <v>56.10688129770523</v>
       </c>
       <c r="C5" t="n">
-        <v>99.77011044408214</v>
+        <v>89.6335653977338</v>
       </c>
       <c r="D5" t="n">
-        <v>103.9179944945249</v>
+        <v>73.41018458505526</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.98626519880311</v>
+        <v>58.64666260859173</v>
       </c>
       <c r="C6" t="n">
-        <v>122.2845305455742</v>
+        <v>112.3423715446668</v>
       </c>
       <c r="D6" t="n">
-        <v>68.2265567066321</v>
+        <v>49.59004003691489</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.38731698375453</v>
+        <v>49.46633982617978</v>
       </c>
       <c r="C7" t="n">
-        <v>126.4805202335251</v>
+        <v>115.1619509512636</v>
       </c>
       <c r="D7" t="n">
-        <v>46.83132898798135</v>
+        <v>41.14210104187108</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.94835258676919</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="C8" t="n">
-        <v>106.814150222053</v>
+        <v>88.8727109269425</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.31562403914873</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>68.44843168779184</v>
+        <v>57.68749510154256</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>42.13661146627311</v>
+        <v>38.00836236991527</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.845077323661437</v>
+        <v>7.892606252716431</v>
       </c>
       <c r="C21" t="n">
-        <v>101.9860052075987</v>
+        <v>104.5770328484927</v>
       </c>
       <c r="D21" t="n">
-        <v>8.825711989119116</v>
+        <v>9.865757815895538</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.123561342014856</v>
+        <v>9.695740327141499</v>
       </c>
       <c r="C2" t="n">
-        <v>15.45467236025329</v>
+        <v>13.70028921276424</v>
       </c>
       <c r="D2" t="n">
-        <v>30.07584091960104</v>
+        <v>22.66266400483337</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.17844140246144</v>
+        <v>27.36621725587984</v>
       </c>
       <c r="C3" t="n">
-        <v>28.05834938737384</v>
+        <v>38.0279973240002</v>
       </c>
       <c r="D3" t="n">
-        <v>90.6300393175443</v>
+        <v>62.74840451693489</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.16656261901924</v>
+        <v>43.75060469205486</v>
       </c>
       <c r="C4" t="n">
-        <v>64.18371966054373</v>
+        <v>67.45097602027711</v>
       </c>
       <c r="D4" t="n">
-        <v>134.7870875591573</v>
+        <v>99.90657337497241</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.1238898038469</v>
+        <v>58.1930951692297</v>
       </c>
       <c r="C5" t="n">
-        <v>107.3050240741764</v>
+        <v>101.3163630782709</v>
       </c>
       <c r="D5" t="n">
-        <v>120.2640937702343</v>
+        <v>87.69461368184635</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.42023874180921</v>
+        <v>66.1334706011779</v>
       </c>
       <c r="C6" t="n">
-        <v>138.2241862717254</v>
+        <v>124.8203848656437</v>
       </c>
       <c r="D6" t="n">
-        <v>80.38255678061611</v>
+        <v>58.6064109527176</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.65166915810418</v>
+        <v>59.16797063954677</v>
       </c>
       <c r="C7" t="n">
-        <v>147.4408337191945</v>
+        <v>135.8827179970968</v>
       </c>
       <c r="D7" t="n">
-        <v>53.35896947351839</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.70906818884022</v>
+        <v>40.97324043674063</v>
       </c>
       <c r="C8" t="n">
-        <v>133.9349305518711</v>
+        <v>118.2466022380071</v>
       </c>
       <c r="D8" t="n">
-        <v>41.8911745402114</v>
+        <v>39.80496066868692</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.19687362466387</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="C9" t="n">
-        <v>95.07342942696533</v>
+        <v>80.76249314215958</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>37.38593432542277</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>58.2225476003571</v>
+        <v>51.67429041303087</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>39.44858625204532</v>
+        <v>37.6716229073586</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.008309201457923</v>
+        <v>8.064434796865466</v>
       </c>
       <c r="C21" t="n">
-        <v>110.1142515200465</v>
+        <v>112.9020871561165</v>
       </c>
       <c r="D21" t="n">
-        <v>10.0103865018224</v>
+        <v>11.08859784569002</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.557092916664446</v>
+        <v>8.887761966546375</v>
       </c>
       <c r="C2" t="n">
-        <v>10.50862742625786</v>
+        <v>9.205848222722341</v>
       </c>
       <c r="D2" t="n">
-        <v>24.9305012016435</v>
+        <v>18.43034965182537</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.3003991019663</v>
+        <v>32.05406254365836</v>
       </c>
       <c r="C3" t="n">
-        <v>46.39739650270426</v>
+        <v>55.48347150550849</v>
       </c>
       <c r="D3" t="n">
-        <v>98.57728698342224</v>
+        <v>70.17041716104077</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.64106555533994</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="C4" t="n">
-        <v>88.6753796383889</v>
+        <v>88.77748139963056</v>
       </c>
       <c r="D4" t="n">
-        <v>131.2135259156989</v>
+        <v>97.25192758268904</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.65507206510666</v>
+        <v>37.25732537616646</v>
       </c>
       <c r="C5" t="n">
-        <v>82.58952561976294</v>
+        <v>74.56373813754526</v>
       </c>
       <c r="D5" t="n">
-        <v>80.35604959260144</v>
+        <v>59.42027979953821</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.94094057349173</v>
+        <v>36.70951015719674</v>
       </c>
       <c r="C6" t="n">
-        <v>97.08699396837559</v>
+        <v>89.47943100816705</v>
       </c>
       <c r="D6" t="n">
-        <v>35.13969557810609</v>
+        <v>29.94723197034471</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>27.12863431145211</v>
       </c>
       <c r="C7" t="n">
-        <v>94.14175085563514</v>
+        <v>83.12261462316894</v>
       </c>
       <c r="D7" t="n">
-        <v>29.40432548989622</v>
+        <v>27.96704685087888</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="C8" t="n">
-        <v>70.01333752836128</v>
+        <v>59.49881961587794</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>44.37499623195582</v>
+        <v>39.38280915586078</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.965278977452867</v>
+        <v>5.64504929941916</v>
       </c>
       <c r="C2" t="n">
-        <v>5.071708640139023</v>
+        <v>3.912264601423539</v>
       </c>
       <c r="D2" t="n">
-        <v>17.56248468127119</v>
+        <v>12.84027822384403</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.02689240310894</v>
+        <v>32.32404316232623</v>
       </c>
       <c r="C3" t="n">
-        <v>44.59588946541136</v>
+        <v>46.14705083812132</v>
       </c>
       <c r="D3" t="n">
-        <v>97.3893722612836</v>
+        <v>69.85134915716056</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.2559016601057</v>
+        <v>42.4615699563788</v>
       </c>
       <c r="C4" t="n">
-        <v>104.105508306036</v>
+        <v>116.957567502331</v>
       </c>
       <c r="D4" t="n">
-        <v>146.4905019414836</v>
+        <v>109.2361218084298</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.89483948912113</v>
+        <v>41.50338419703392</v>
       </c>
       <c r="C5" t="n">
-        <v>121.1231230114503</v>
+        <v>117.196132194463</v>
       </c>
       <c r="D5" t="n">
-        <v>100.899120303966</v>
+        <v>74.66191290796993</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.13340418125311</v>
+        <v>43.47178834404877</v>
       </c>
       <c r="C6" t="n">
-        <v>116.2467821644563</v>
+        <v>105.660596669563</v>
       </c>
       <c r="D6" t="n">
-        <v>45.00135126726531</v>
+        <v>36.91076843656734</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.22360179685679</v>
+        <v>25.81112889235289</v>
       </c>
       <c r="C7" t="n">
-        <v>114.7427446815502</v>
+        <v>104.6219075984698</v>
       </c>
       <c r="D7" t="n">
-        <v>32.33876937788993</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>12.35038611942487</v>
       </c>
       <c r="C8" t="n">
-        <v>90.95892479846698</v>
+        <v>77.52370746584938</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>49.25624581747095</v>
+        <v>46.14999608123405</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.963315482044373</v>
+        <v>5.443791020048564</v>
       </c>
       <c r="C2" t="n">
-        <v>5.948409340031424</v>
+        <v>3.602032326881548</v>
       </c>
       <c r="D2" t="n">
-        <v>18.65615162380214</v>
+        <v>14.08906130364598</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2359636063845</v>
+        <v>25.62852381936298</v>
       </c>
       <c r="C3" t="n">
-        <v>31.52391878336508</v>
+        <v>29.55551463635023</v>
       </c>
       <c r="D3" t="n">
-        <v>89.54029936583034</v>
+        <v>64.23084355034757</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.15227837181205</v>
+        <v>52.4930679983727</v>
       </c>
       <c r="C4" t="n">
-        <v>107.7301208301152</v>
+        <v>116.0258889310008</v>
       </c>
       <c r="D4" t="n">
-        <v>159.4446628990202</v>
+        <v>118.4125176000248</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.00621894805753</v>
+        <v>51.98354093986863</v>
       </c>
       <c r="C5" t="n">
-        <v>156.9569142164588</v>
+        <v>166.4553232550467</v>
       </c>
       <c r="D5" t="n">
-        <v>125.5900750657732</v>
+        <v>94.46867284114934</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.92964262712628</v>
+        <v>50.15356321915257</v>
       </c>
       <c r="C6" t="n">
-        <v>151.5072327101848</v>
+        <v>145.509735984941</v>
       </c>
       <c r="D6" t="n">
-        <v>61.7460401108989</v>
+        <v>49.54978838104078</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.60772719112455</v>
+        <v>36.4110588551057</v>
       </c>
       <c r="C7" t="n">
-        <v>140.9131932336574</v>
+        <v>128.7562114119692</v>
       </c>
       <c r="D7" t="n">
-        <v>36.71049190490098</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="C8" t="n">
-        <v>119.4983305609218</v>
+        <v>106.3134588928871</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>76.32499351896399</v>
+        <v>68.22655670663207</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
         <v>11.33329549782518</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.359139733305085</v>
+        <v>3.230931694676253</v>
       </c>
       <c r="C2" t="n">
-        <v>2.796017461694916</v>
+        <v>1.670934592628071</v>
       </c>
       <c r="D2" t="n">
-        <v>13.02190154912969</v>
+        <v>9.767407909551517</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.11324514335365</v>
+        <v>25.08856258202724</v>
       </c>
       <c r="C3" t="n">
-        <v>29.96293993361266</v>
+        <v>24.63695863807371</v>
       </c>
       <c r="D3" t="n">
-        <v>87.92041565382311</v>
+        <v>63.38163178617408</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.73860273542564</v>
+        <v>57.98103766511237</v>
       </c>
       <c r="C4" t="n">
-        <v>107.411052826235</v>
+        <v>111.5844623169882</v>
       </c>
       <c r="D4" t="n">
-        <v>169.2081438177547</v>
+        <v>125.1512338419749</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.16606389740051</v>
+        <v>54.43791020048565</v>
       </c>
       <c r="C5" t="n">
-        <v>192.3243752619502</v>
+        <v>201.3319104484147</v>
       </c>
       <c r="D5" t="n">
-        <v>132.2414157620454</v>
+        <v>102.6908098642164</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.36862271964485</v>
+        <v>43.43153668817465</v>
       </c>
       <c r="C6" t="n">
-        <v>181.615471304026</v>
+        <v>181.4947163364036</v>
       </c>
       <c r="D6" t="n">
-        <v>59.89446394068941</v>
+        <v>48.5434969841878</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>12.27675504160636</v>
       </c>
       <c r="C7" t="n">
-        <v>151.8724428561646</v>
+        <v>137.8589761257456</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>34.2551408965797</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>92.54444734082557</v>
+        <v>83.61545197070083</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
         <v>9.506263020221864</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.661518026213103</v>
+        <v>4.974515617418588</v>
       </c>
       <c r="C2" t="n">
-        <v>5.502695882303372</v>
+        <v>5.549819772107219</v>
       </c>
       <c r="D2" t="n">
-        <v>17.50750680983337</v>
+        <v>10.26809923871739</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.27813769993811</v>
+        <v>18.25068982194821</v>
       </c>
       <c r="C3" t="n">
-        <v>20.25836387713293</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="D3" t="n">
-        <v>79.75227475448963</v>
+        <v>57.1426251256856</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.19882142453914</v>
+        <v>53.34817024877168</v>
       </c>
       <c r="C4" t="n">
-        <v>92.32551760277855</v>
+        <v>86.4419036112274</v>
       </c>
       <c r="D4" t="n">
-        <v>173.1773497860246</v>
+        <v>127.8058796342583</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.24093876483053</v>
+        <v>68.84505776030758</v>
       </c>
       <c r="C5" t="n">
-        <v>194.606938674324</v>
+        <v>205.1607264949772</v>
       </c>
       <c r="D5" t="n">
-        <v>156.0242538974244</v>
+        <v>120.7549676223577</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.30449032369931</v>
+        <v>56.11080828852221</v>
       </c>
       <c r="C6" t="n">
-        <v>239.9803723214989</v>
+        <v>245.776610767372</v>
       </c>
       <c r="D6" t="n">
-        <v>80.18129850124551</v>
+        <v>65.61019907481435</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>25.51169584255761</v>
       </c>
       <c r="C7" t="n">
-        <v>199.6619576034908</v>
+        <v>194.8710288067664</v>
       </c>
       <c r="D7" t="n">
-        <v>42.93869934064274</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>137.4397698560322</v>
+        <v>125.5900750657732</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>63.34530712111692</v>
+        <v>59.57343244140068</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
         <v>23.63361248433346</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.876119862815655</v>
+        <v>3.542145716922492</v>
       </c>
       <c r="C2" t="n">
-        <v>3.059125846433061</v>
+        <v>3.2319134423805</v>
       </c>
       <c r="D2" t="n">
-        <v>12.84322346695677</v>
+        <v>8.738536315500859</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.64352777236717</v>
+        <v>17.89235190989812</v>
       </c>
       <c r="C3" t="n">
-        <v>20.9603134856694</v>
+        <v>18.54521413322225</v>
       </c>
       <c r="D3" t="n">
-        <v>76.3456102207532</v>
+        <v>53.33344403320797</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.20409001595887</v>
+        <v>47.52836985799659</v>
       </c>
       <c r="C4" t="n">
-        <v>77.07406701730434</v>
+        <v>67.79556946446775</v>
       </c>
       <c r="D4" t="n">
-        <v>175.8192328581528</v>
+        <v>127.9335068358104</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.14338588921161</v>
+        <v>74.80917506360696</v>
       </c>
       <c r="C5" t="n">
-        <v>190.0908992347887</v>
+        <v>192.5943558806181</v>
       </c>
       <c r="D5" t="n">
-        <v>171.4622365467055</v>
+        <v>133.7876683962341</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.91205328390785</v>
+        <v>67.01900703040852</v>
       </c>
       <c r="C6" t="n">
-        <v>276.7703857904439</v>
+        <v>284.8207169652676</v>
       </c>
       <c r="D6" t="n">
-        <v>96.72472906550851</v>
+        <v>77.52468921355364</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>23.95464398362217</v>
       </c>
       <c r="C7" t="n">
-        <v>248.2898848902438</v>
+        <v>251.6435350479509</v>
       </c>
       <c r="D7" t="n">
-        <v>48.20872101703962</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>175.2419652080556</v>
+        <v>162.6412334240478</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>71.44374393344886</v>
+        <v>70.88905648054941</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.192643534210627</v>
+        <v>5.148284961070273</v>
       </c>
       <c r="C2" t="n">
-        <v>13.14069302134356</v>
+        <v>5.345616249623882</v>
       </c>
       <c r="D2" t="n">
-        <v>10.76879056788326</v>
+        <v>9.176395791594937</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.144979865059039</v>
+        <v>14.98637870532756</v>
       </c>
       <c r="C3" t="n">
-        <v>16.65044106402591</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="D3" t="n">
-        <v>70.00352005131882</v>
+        <v>48.75849973141784</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.55020498720149</v>
+        <v>41.38950146334128</v>
       </c>
       <c r="C4" t="n">
-        <v>65.9322123218073</v>
+        <v>57.91722406433633</v>
       </c>
       <c r="D4" t="n">
-        <v>173.7389094728538</v>
+        <v>125.585166327252</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.98983233672161</v>
+        <v>73.45927197026759</v>
       </c>
       <c r="C5" t="n">
-        <v>169.2533042121501</v>
+        <v>162.896487827152</v>
       </c>
       <c r="D5" t="n">
-        <v>188.6428213710246</v>
+        <v>143.5069706682775</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.6064109527176</v>
+        <v>80.22155015711964</v>
       </c>
       <c r="C6" t="n">
-        <v>287.8395911558266</v>
+        <v>294.5616176868045</v>
       </c>
       <c r="D6" t="n">
-        <v>118.500874893407</v>
+        <v>95.55743104515906</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.08115056874977</v>
+        <v>43.05847256056086</v>
       </c>
       <c r="C7" t="n">
-        <v>311.4702583970473</v>
+        <v>317.2792595630757</v>
       </c>
       <c r="D7" t="n">
-        <v>58.92842419971054</v>
+        <v>52.04146405441917</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>12.35038611942487</v>
       </c>
       <c r="C8" t="n">
-        <v>233.6559536107408</v>
+        <v>232.3207767329652</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>124.2499894494763</v>
+        <v>119.9234273168606</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>50.96252332745193</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.89441321629785</v>
+        <v>8.282023633026093</v>
       </c>
       <c r="C2" t="n">
-        <v>9.376672323261285</v>
+        <v>5.609706382066275</v>
       </c>
       <c r="D2" t="n">
-        <v>19.2697439389564</v>
+        <v>5.229770020522759</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.309070600388498</v>
+        <v>3.645229225868407</v>
       </c>
       <c r="C2" t="n">
-        <v>7.568293052038661</v>
+        <v>3.035563901531138</v>
       </c>
       <c r="D2" t="n">
-        <v>7.926630964088747</v>
+        <v>6.754424205218055</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.62036673809275</v>
+        <v>20.2534551386117</v>
       </c>
       <c r="C3" t="n">
-        <v>29.09900195387546</v>
+        <v>19.53187057599029</v>
       </c>
       <c r="D3" t="n">
-        <v>75.13806054452964</v>
+        <v>52.98983233672159</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.02389040673396</v>
+        <v>56.44951124648735</v>
       </c>
       <c r="C4" t="n">
-        <v>95.32475683925254</v>
+        <v>85.90586936470865</v>
       </c>
       <c r="D4" t="n">
-        <v>178.6525567326091</v>
+        <v>129.3118806125729</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.99301425954582</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="C5" t="n">
-        <v>246.4432174585556</v>
+        <v>245.3878386764903</v>
       </c>
       <c r="D5" t="n">
-        <v>171.2167996206437</v>
+        <v>133.2477071588984</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.28054316370311</v>
+        <v>26.72709950041517</v>
       </c>
       <c r="C6" t="n">
-        <v>261.5552598700268</v>
+        <v>269.6055910448507</v>
       </c>
       <c r="D6" t="n">
-        <v>91.81402704886597</v>
+        <v>76.63915278432302</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>164.3288577276481</v>
+        <v>163.3706719683032</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>91.54306468249383</v>
+        <v>88.37201959777664</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>25.20146356801562</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>38.82812170296133</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
         <v>19.07535789351553</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.074473956802516</v>
+        <v>9.012443924985719</v>
       </c>
       <c r="C2" t="n">
-        <v>5.133558745506572</v>
+        <v>5.362305960596078</v>
       </c>
       <c r="D2" t="n">
-        <v>23.03081939392592</v>
+        <v>8.58440192593411</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.52219196766807</v>
+        <v>17.58310138306037</v>
       </c>
       <c r="C3" t="n">
-        <v>23.62575850269949</v>
+        <v>14.13225820263284</v>
       </c>
       <c r="D3" t="n">
-        <v>19.32079481957723</v>
+        <v>7.530004891573036</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39607697240599</v>
+        <v>13.39871984264622</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13240297318431</v>
+        <v>70.14623917620671</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576009055577176</v>
+        <v>1.576319981487791</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.734969177582366</v>
+        <v>5.283766144256333</v>
       </c>
       <c r="C2" t="n">
-        <v>3.564725914120168</v>
+        <v>3.413536767666159</v>
       </c>
       <c r="D2" t="n">
-        <v>24.55645532632547</v>
+        <v>17.16389511334699</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.65949777754238</v>
+        <v>25.72178985126643</v>
       </c>
       <c r="C3" t="n">
-        <v>21.36773878293183</v>
+        <v>18.58939277991335</v>
       </c>
       <c r="D3" t="n">
-        <v>33.99792299806705</v>
+        <v>12.91979978788802</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.57502641724815</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="C4" t="n">
-        <v>36.55243052451725</v>
+        <v>22.06674314835556</v>
       </c>
       <c r="D4" t="n">
-        <v>25.19360958638165</v>
+        <v>19.01645303126072</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43495119701179</v>
+        <v>15.44319237810863</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11078036227633</v>
+        <v>86.15675747786919</v>
       </c>
       <c r="D21" t="n">
-        <v>3.24946340989722</v>
+        <v>3.25119839539129</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.82921695719006</v>
+        <v>5.038329218194631</v>
       </c>
       <c r="C2" t="n">
-        <v>5.732424845097126</v>
+        <v>6.200718500022854</v>
       </c>
       <c r="D2" t="n">
-        <v>34.60366133158733</v>
+        <v>25.32320028334223</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.81872083207961</v>
+        <v>21.52972715413255</v>
       </c>
       <c r="C3" t="n">
-        <v>16.8811517745239</v>
+        <v>15.36926030998382</v>
       </c>
       <c r="D3" t="n">
-        <v>45.7543517564226</v>
+        <v>23.65030219530566</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.91206897944107</v>
+        <v>36.90978668886309</v>
       </c>
       <c r="C4" t="n">
-        <v>46.02236887968198</v>
+        <v>36.475854203586</v>
       </c>
       <c r="D4" t="n">
-        <v>36.55243052451725</v>
+        <v>21.22440361811179</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.73817646260237</v>
+        <v>17.47510913559323</v>
       </c>
       <c r="C5" t="n">
-        <v>40.84070449666732</v>
+        <v>25.50089661781091</v>
       </c>
       <c r="D5" t="n">
-        <v>31.68590715456581</v>
+        <v>29.30516897176729</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.39751000922872</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.2069942013426</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.722715668255</v>
+        <v>16.73882905491661</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0085655763555</v>
+        <v>102.1068572349913</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180678917063751</v>
+        <v>5.021648716474983</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.120796025351362</v>
+        <v>5.166938167450963</v>
       </c>
       <c r="C2" t="n">
-        <v>5.462444226429254</v>
+        <v>5.290638378186061</v>
       </c>
       <c r="D2" t="n">
-        <v>30.39294542807275</v>
+        <v>24.7626223442173</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.0824100538945</v>
+        <v>19.19316761802514</v>
       </c>
       <c r="C3" t="n">
-        <v>19.90002596508285</v>
+        <v>20.38108234016379</v>
       </c>
       <c r="D3" t="n">
-        <v>61.87464906015522</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.23037621979529</v>
+        <v>39.70482240285375</v>
       </c>
       <c r="C4" t="n">
-        <v>43.49535028895069</v>
+        <v>37.2288546927433</v>
       </c>
       <c r="D4" t="n">
-        <v>50.46379549369455</v>
+        <v>27.91206897944107</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.26804248545517</v>
+        <v>36.25103397931348</v>
       </c>
       <c r="C5" t="n">
-        <v>64.69717370986481</v>
+        <v>48.52288028239862</v>
       </c>
       <c r="D5" t="n">
-        <v>37.08551952792327</v>
+        <v>30.11511082777092</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.47172192412398</v>
+        <v>14.81260936167588</v>
       </c>
       <c r="C6" t="n">
-        <v>39.48687441251096</v>
+        <v>27.12961605915636</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.743445054022093</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.40016181936776</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03938146227341</v>
+        <v>18.06703823619285</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6854885872122</v>
+        <v>117.8659161123057</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013127154091136</v>
+        <v>6.88268123283537</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.998478472948011</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C2" t="n">
-        <v>7.933503198018475</v>
+        <v>5.020657759518188</v>
       </c>
       <c r="D2" t="n">
-        <v>26.90970457340507</v>
+        <v>28.42159603794516</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.55088363526948</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="C3" t="n">
-        <v>19.35515598922587</v>
+        <v>19.23734626471625</v>
       </c>
       <c r="D3" t="n">
-        <v>66.99446333780234</v>
+        <v>45.23402547317179</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.18986252201391</v>
+        <v>27.6695772964921</v>
       </c>
       <c r="C4" t="n">
-        <v>38.90077103307561</v>
+        <v>37.33095645398497</v>
       </c>
       <c r="D4" t="n">
-        <v>60.27832729304991</v>
+        <v>34.53592073999429</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.58019719767664</v>
+        <v>29.45243112740432</v>
       </c>
       <c r="C5" t="n">
-        <v>54.3151917374548</v>
+        <v>44.32590884674349</v>
       </c>
       <c r="D5" t="n">
-        <v>37.20823799095412</v>
+        <v>27.14532402242431</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.20254312671111</v>
+        <v>17.67047692873834</v>
       </c>
       <c r="C6" t="n">
-        <v>48.74475526355839</v>
+        <v>35.90447703971436</v>
       </c>
       <c r="D6" t="n">
-        <v>32.28182801104362</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>24.852943133008</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,10 +5997,10 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.047245906990762</v>
+        <v>7.062850794885268</v>
       </c>
       <c r="C21" t="n">
-        <v>66.0679303780384</v>
+        <v>66.21422620204939</v>
       </c>
       <c r="D21" t="n">
-        <v>4.404528691869226</v>
+        <v>5.297138096163951</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.10017932356218</v>
+        <v>6.93801102591221</v>
       </c>
       <c r="C2" t="n">
-        <v>5.917975161199774</v>
+        <v>7.032258805519903</v>
       </c>
       <c r="D2" t="n">
-        <v>23.67680938332033</v>
+        <v>21.30097993904305</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.83482970597506</v>
+        <v>21.622993186036</v>
       </c>
       <c r="C3" t="n">
-        <v>26.86552592671396</v>
+        <v>19.49750940634166</v>
       </c>
       <c r="D3" t="n">
-        <v>73.41018458505525</v>
+        <v>58.88031856220246</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.59300097556086</v>
+        <v>30.71986741358695</v>
       </c>
       <c r="C4" t="n">
-        <v>44.98858854711009</v>
+        <v>44.33768981919445</v>
       </c>
       <c r="D4" t="n">
-        <v>80.82630674293564</v>
+        <v>51.02535518052373</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.01693605734623</v>
+        <v>37.15915060574178</v>
       </c>
       <c r="C5" t="n">
-        <v>65.16350386938205</v>
+        <v>59.73934780341843</v>
       </c>
       <c r="D5" t="n">
-        <v>51.93445355465628</v>
+        <v>34.21390749300135</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.2252054393668</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>70.96366930607222</v>
+        <v>56.63407981488576</v>
       </c>
       <c r="D6" t="n">
-        <v>37.31328499530853</v>
+        <v>32.40258297866598</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.25868267230242</v>
+        <v>14.85187926984575</v>
       </c>
       <c r="C7" t="n">
-        <v>51.44259795482861</v>
+        <v>38.5669768136317</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>27.20422888467911</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,10 +6305,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.26665558019207</v>
+        <v>7.288629761557833</v>
       </c>
       <c r="C21" t="n">
-        <v>75.39155164449274</v>
+        <v>76.53061249635725</v>
       </c>
       <c r="D21" t="n">
-        <v>5.449991685144053</v>
+        <v>6.377551041363104</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.107632394568655</v>
+        <v>5.896376711706344</v>
       </c>
       <c r="C2" t="n">
-        <v>8.295768100885548</v>
+        <v>7.883434065101888</v>
       </c>
       <c r="D2" t="n">
-        <v>29.07642175667778</v>
+        <v>17.18156657202343</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.17705874412969</v>
+        <v>23.08579726536375</v>
       </c>
       <c r="C3" t="n">
-        <v>24.55841882173396</v>
+        <v>24.3620692808846</v>
       </c>
       <c r="D3" t="n">
-        <v>75.31968386981529</v>
+        <v>62.25753066481148</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.9022925601276</v>
+        <v>37.54792269662352</v>
       </c>
       <c r="C4" t="n">
-        <v>57.45776613874882</v>
+        <v>47.06891193240908</v>
       </c>
       <c r="D4" t="n">
-        <v>99.48540360985054</v>
+        <v>68.57409539393547</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.20194659410114</v>
+        <v>42.3378697456437</v>
       </c>
       <c r="C5" t="n">
-        <v>75.47185476397355</v>
+        <v>72.69841749947632</v>
       </c>
       <c r="D5" t="n">
-        <v>68.72233929727673</v>
+        <v>45.43037501402116</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.92585450502953</v>
+        <v>42.10323204432872</v>
       </c>
       <c r="C6" t="n">
-        <v>89.07691444942586</v>
+        <v>77.645444181176</v>
       </c>
       <c r="D6" t="n">
-        <v>45.48437113775474</v>
+        <v>36.26674194258143</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>26.70942804173872</v>
       </c>
       <c r="C7" t="n">
-        <v>79.52941802562562</v>
+        <v>63.12048689684442</v>
       </c>
       <c r="D7" t="n">
-        <v>37.06981156465531</v>
+        <v>35.15344004596554</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C8" t="n">
-        <v>49.15119881311656</v>
+        <v>39.13737222979909</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>27.17968519207294</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.473928959923118</v>
+        <v>7.503160985540522</v>
       </c>
       <c r="C21" t="n">
-        <v>85.01594191912547</v>
+        <v>86.286351333716</v>
       </c>
       <c r="D21" t="n">
-        <v>6.539687839932729</v>
+        <v>7.503160985540522</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_74_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497625442496</v>
+        <v>10.84497631877866</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907167085168</v>
+        <v>37.78907189509066</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.784678457600458</v>
+        <v>1.377392029058275</v>
       </c>
       <c r="C2" t="n">
-        <v>8.161268665403735</v>
+        <v>2.029272504678157</v>
       </c>
       <c r="D2" t="n">
-        <v>16.21552683104457</v>
+        <v>19.30705035171777</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.50518346152638</v>
+        <v>10.99557428756428</v>
       </c>
       <c r="C3" t="n">
-        <v>27.94544840138546</v>
+        <v>35.36255230697011</v>
       </c>
       <c r="D3" t="n">
-        <v>61.4672237628928</v>
+        <v>69.37029278207962</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.61923042613503</v>
+        <v>18.48041878474196</v>
       </c>
       <c r="C4" t="n">
-        <v>54.82864578677587</v>
+        <v>128.4950665226395</v>
       </c>
       <c r="D4" t="n">
-        <v>83.50647797552944</v>
+        <v>64.91119470939061</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.57825906446394</v>
+        <v>18.8986433067511</v>
       </c>
       <c r="C5" t="n">
-        <v>79.71791358484101</v>
+        <v>132.5850274585318</v>
       </c>
       <c r="D5" t="n">
-        <v>58.53670686571608</v>
+        <v>43.36870483510285</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.75733805726436</v>
+        <v>12.51826497685108</v>
       </c>
       <c r="C6" t="n">
-        <v>97.93227874173209</v>
+        <v>65.77120569831082</v>
       </c>
       <c r="D6" t="n">
-        <v>42.34474197957343</v>
+        <v>29.26295382048468</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.86640986342697</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>89.23104883899259</v>
+        <v>34.85400699617026</v>
       </c>
       <c r="D7" t="n">
-        <v>37.54890444432775</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.69524160552276</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>62.16917337142927</v>
+        <v>28.03871443328891</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.985936736971052</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>38.82812170296133</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.704944597242512</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.34868939087609</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.668062671897825</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.033060626774903</v>
+        <v>1.303760951239764</v>
       </c>
       <c r="C2" t="n">
-        <v>12.14912784005428</v>
+        <v>2.638937829015426</v>
       </c>
       <c r="D2" t="n">
-        <v>22.37501192748906</v>
+        <v>15.07866298952676</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.54998400302324</v>
+        <v>7.647814616082653</v>
       </c>
       <c r="C3" t="n">
-        <v>29.85003894762427</v>
+        <v>19.22262004915255</v>
       </c>
       <c r="D3" t="n">
-        <v>60.05841580729863</v>
+        <v>68.61434704980958</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.04490801915065</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="C4" t="n">
-        <v>62.58837964114265</v>
+        <v>107.0536966618892</v>
       </c>
       <c r="D4" t="n">
-        <v>94.15058658497337</v>
+        <v>83.99146134142737</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>23.48831382410494</v>
+      </c>
+      <c r="C5" t="n">
+        <v>190.4590546238812</v>
+      </c>
+      <c r="D5" t="n">
         <v>56.10688129770523</v>
-      </c>
-      <c r="C5" t="n">
-        <v>89.6335653977338</v>
-      </c>
-      <c r="D5" t="n">
-        <v>73.41018458505526</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.64666260859173</v>
+        <v>18.8377749490878</v>
       </c>
       <c r="C6" t="n">
-        <v>112.3423715446668</v>
+        <v>139.3109809803267</v>
       </c>
       <c r="D6" t="n">
-        <v>49.59004003691489</v>
+        <v>35.66296710446964</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.46633982617978</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>115.1619509512636</v>
+        <v>65.39617807528853</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.2097595180061</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>88.8727109269425</v>
+        <v>37.80219535202343</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>57.68749510154256</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>38.00836236991527</v>
+        <v>35.16129402759952</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.892606252716431</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5770328484927</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.865757815895538</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.695740327141499</v>
+        <v>0.6921321314940013</v>
       </c>
       <c r="C2" t="n">
-        <v>13.70028921276424</v>
+        <v>1.129991607588079</v>
       </c>
       <c r="D2" t="n">
-        <v>22.66266400483337</v>
+        <v>10.29264293132356</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.36621725587984</v>
+        <v>7.048948516492098</v>
       </c>
       <c r="C3" t="n">
-        <v>38.0279973240002</v>
+        <v>16.13502351929633</v>
       </c>
       <c r="D3" t="n">
-        <v>62.74840451693489</v>
+        <v>67.66696051521141</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.75060469205486</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="C4" t="n">
-        <v>67.45097602027711</v>
+        <v>93.1806198531775</v>
       </c>
       <c r="D4" t="n">
-        <v>99.90657337497241</v>
+        <v>95.42685860049421</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.1930951692297</v>
+        <v>23.73375075016664</v>
       </c>
       <c r="C5" t="n">
-        <v>101.3163630782709</v>
+        <v>218.0461651132166</v>
       </c>
       <c r="D5" t="n">
-        <v>87.69461368184635</v>
+        <v>63.51907646476864</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.1334706011779</v>
+        <v>14.61135108230528</v>
       </c>
       <c r="C6" t="n">
-        <v>124.8203848656437</v>
+        <v>181.1324514335365</v>
       </c>
       <c r="D6" t="n">
-        <v>58.6064109527176</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>59.16797063954677</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>135.8827179970968</v>
+        <v>63.77923960639403</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>40.97324043674063</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>118.2466022380071</v>
+        <v>38.63668090063322</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21.74374815365835</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>80.76249314215958</v>
+        <v>26.84687272033327</v>
       </c>
       <c r="D9" t="n">
-        <v>37.38593432542277</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>51.67429041303087</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.6716229073586</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.064434796865466</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112.9020871561165</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08859784569002</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.887761966546375</v>
+        <v>0.8001243789611505</v>
       </c>
       <c r="C2" t="n">
-        <v>9.205848222722341</v>
+        <v>3.562762418711675</v>
       </c>
       <c r="D2" t="n">
-        <v>18.43034965182537</v>
+        <v>15.5135772225081</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>32.05406254365836</v>
+        <v>4.60439673291754</v>
       </c>
       <c r="C3" t="n">
-        <v>55.48347150550849</v>
+        <v>9.454230391896784</v>
       </c>
       <c r="D3" t="n">
-        <v>70.17041716104077</v>
+        <v>61.08925089675778</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.95035713990669</v>
+        <v>18.21240166148258</v>
       </c>
       <c r="C4" t="n">
-        <v>88.77748139963056</v>
+        <v>65.07711007140833</v>
       </c>
       <c r="D4" t="n">
-        <v>97.25192758268904</v>
+        <v>106.428323374284</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.25732537616646</v>
+        <v>28.56885819358219</v>
       </c>
       <c r="C5" t="n">
-        <v>74.56373813754526</v>
+        <v>198.2884925652496</v>
       </c>
       <c r="D5" t="n">
-        <v>59.42027979953821</v>
+        <v>81.16599144860506</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.70951015719674</v>
+        <v>22.25916569838794</v>
       </c>
       <c r="C6" t="n">
-        <v>89.47943100816705</v>
+        <v>262.4005446433833</v>
       </c>
       <c r="D6" t="n">
-        <v>29.94723197034471</v>
+        <v>46.77242412572655</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.12863431145211</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>83.12261462316894</v>
+        <v>155.7051858935441</v>
       </c>
       <c r="D7" t="n">
-        <v>27.96704685087888</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.10418842983718</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
         <v>59.49881961587794</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>39.38280915586078</v>
+        <v>36.72030938194344</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.51009220004762</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.89551813718911</v>
-      </c>
-      <c r="D14" t="n">
-        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.64504929941916</v>
+        <v>0.4869468613064179</v>
       </c>
       <c r="C2" t="n">
-        <v>3.912264601423539</v>
+        <v>2.32085157283946</v>
       </c>
       <c r="D2" t="n">
-        <v>12.84027822384403</v>
+        <v>12.13636511989907</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>32.32404316232623</v>
+        <v>3.82881604656256</v>
       </c>
       <c r="C3" t="n">
-        <v>46.14705083812132</v>
+        <v>11.84478605173777</v>
       </c>
       <c r="D3" t="n">
-        <v>69.85134915716056</v>
+        <v>59.80807014271569</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.4615699563788</v>
+        <v>14.89409442112836</v>
       </c>
       <c r="C4" t="n">
-        <v>116.957567502331</v>
+        <v>46.92852201070178</v>
       </c>
       <c r="D4" t="n">
-        <v>109.2361218084298</v>
+        <v>113.281904097631</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.50338419703392</v>
+        <v>29.94330497952772</v>
       </c>
       <c r="C5" t="n">
-        <v>117.196132194463</v>
+        <v>171.5849550097363</v>
       </c>
       <c r="D5" t="n">
-        <v>74.66191290796993</v>
+        <v>94.88591561545424</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.47178834404877</v>
+        <v>27.33087433852696</v>
       </c>
       <c r="C6" t="n">
-        <v>105.660596669563</v>
+        <v>298.0635117478529</v>
       </c>
       <c r="D6" t="n">
-        <v>36.91076843656734</v>
+        <v>56.67433147075987</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.81112889235289</v>
+        <v>10.06095047312131</v>
       </c>
       <c r="C7" t="n">
-        <v>104.6219075984698</v>
+        <v>233.0187993506847</v>
       </c>
       <c r="D7" t="n">
-        <v>30.48228446915921</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>77.52370746584938</v>
+        <v>95.79894098040376</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>46.14999608123405</v>
+        <v>46.70468353413349</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>32.74128593663113</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.443791020048564</v>
+        <v>0.6852598975642736</v>
       </c>
       <c r="C2" t="n">
-        <v>3.602032326881548</v>
+        <v>6.530585728649783</v>
       </c>
       <c r="D2" t="n">
-        <v>14.08906130364598</v>
+        <v>11.87522023056942</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.62852381936298</v>
+        <v>2.753802310412303</v>
       </c>
       <c r="C3" t="n">
-        <v>29.55551463635023</v>
+        <v>10.32307711015521</v>
       </c>
       <c r="D3" t="n">
-        <v>64.23084355034757</v>
+        <v>55.90562301833462</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.4930679983727</v>
+        <v>11.25671917689393</v>
       </c>
       <c r="C4" t="n">
-        <v>116.0258889310008</v>
+        <v>38.19882142453914</v>
       </c>
       <c r="D4" t="n">
-        <v>118.4125176000248</v>
+        <v>116.7278385395373</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.98354093986863</v>
+        <v>27.243498792849</v>
       </c>
       <c r="C5" t="n">
-        <v>166.4553232550467</v>
+        <v>132.1677846842269</v>
       </c>
       <c r="D5" t="n">
-        <v>94.46867284114934</v>
+        <v>110.8884031946773</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.15356321915257</v>
+        <v>33.04660947265189</v>
       </c>
       <c r="C6" t="n">
-        <v>145.509735984941</v>
+        <v>288.0408494351972</v>
       </c>
       <c r="D6" t="n">
-        <v>49.54978838104078</v>
+        <v>70.15863618858982</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.4110588551057</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="C7" t="n">
-        <v>128.7562114119692</v>
+        <v>323.8667866585718</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>44.85507085933252</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.52557917913731</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>106.3134588928871</v>
+        <v>186.4240715594268</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>68.22655670663207</v>
+        <v>76.32499351896399</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.71093387325747</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>42.42131830050468</v>
+        <v>42.13661146627311</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
         <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.230931694676253</v>
+        <v>0.460439673291754</v>
       </c>
       <c r="C2" t="n">
-        <v>1.670934592628071</v>
+        <v>3.448879685019045</v>
       </c>
       <c r="D2" t="n">
-        <v>9.767407909551517</v>
+        <v>8.551022503989719</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.08856258202724</v>
+        <v>4.000621894805753</v>
       </c>
       <c r="C3" t="n">
-        <v>24.63695863807371</v>
+        <v>17.20512851692535</v>
       </c>
       <c r="D3" t="n">
-        <v>63.38163178617408</v>
+        <v>60.5738333520282</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.98103766511237</v>
+        <v>18.59528326613884</v>
       </c>
       <c r="C4" t="n">
-        <v>111.5844623169882</v>
+        <v>58.6064109527176</v>
       </c>
       <c r="D4" t="n">
-        <v>125.1512338419749</v>
+        <v>119.1782808093373</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.43791020048565</v>
+        <v>20.37126486312132</v>
       </c>
       <c r="C5" t="n">
-        <v>201.3319104484147</v>
+        <v>221.703175311536</v>
       </c>
       <c r="D5" t="n">
-        <v>102.6908098642164</v>
+        <v>102.494460323367</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.43153668817465</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>181.4947163364036</v>
+        <v>283.894928880163</v>
       </c>
       <c r="D6" t="n">
-        <v>48.5434969841878</v>
+        <v>60.17622553180826</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.27675504160636</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>137.8589761257456</v>
+        <v>131.0917892003723</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>83.61545197070083</v>
+        <v>56.24432597629976</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.17187226816797</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>26.62499773917349</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>34.75877746885832</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.974515617418588</v>
+        <v>0.3023782929080176</v>
       </c>
       <c r="C2" t="n">
-        <v>5.549819772107219</v>
+        <v>2.666426764734337</v>
       </c>
       <c r="D2" t="n">
-        <v>10.26809923871739</v>
+        <v>7.099999397112932</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.25068982194821</v>
+        <v>2.77343726449724</v>
       </c>
       <c r="C3" t="n">
-        <v>15.23181563138926</v>
+        <v>15.16800203061322</v>
       </c>
       <c r="D3" t="n">
-        <v>57.1426251256856</v>
+        <v>53.66232951413066</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.34817024877168</v>
+        <v>12.39260127070749</v>
       </c>
       <c r="C4" t="n">
-        <v>86.4419036112274</v>
+        <v>48.86845547429348</v>
       </c>
       <c r="D4" t="n">
-        <v>127.8058796342583</v>
+        <v>117.0724319837279</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.84505776030758</v>
+        <v>19.16862392541898</v>
       </c>
       <c r="C5" t="n">
-        <v>205.1607264949772</v>
+        <v>149.8392433606695</v>
       </c>
       <c r="D5" t="n">
-        <v>120.7549676223577</v>
+        <v>108.826733015759</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.11080828852221</v>
+        <v>11.67298020349458</v>
       </c>
       <c r="C6" t="n">
-        <v>245.776610767372</v>
+        <v>264.6948890282081</v>
       </c>
       <c r="D6" t="n">
-        <v>65.61019907481435</v>
+        <v>63.3963580017378</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.51169584255761</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="C7" t="n">
-        <v>194.8710288067664</v>
+        <v>182.5343871552009</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>125.5900750657732</v>
+        <v>67.92712365683681</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>59.57343244140068</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>21.41093568191868</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.542145716922492</v>
+        <v>0.7471100029318227</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2319134423805</v>
+        <v>6.90070461315083</v>
       </c>
       <c r="D2" t="n">
-        <v>8.738536315500859</v>
+        <v>14.67123769226433</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.89235190989812</v>
+        <v>1.821141991377833</v>
       </c>
       <c r="C3" t="n">
-        <v>18.54521413322225</v>
+        <v>12.26202882604266</v>
       </c>
       <c r="D3" t="n">
-        <v>53.33344403320797</v>
+        <v>46.88827035482766</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.52836985799659</v>
+        <v>8.755226026473055</v>
       </c>
       <c r="C4" t="n">
-        <v>67.79556946446775</v>
+        <v>42.97207876258713</v>
       </c>
       <c r="D4" t="n">
-        <v>127.9335068358104</v>
+        <v>117.81266975273</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.80917506360696</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="C5" t="n">
-        <v>192.5943558806181</v>
+        <v>116.6807146497334</v>
       </c>
       <c r="D5" t="n">
-        <v>133.7876683962341</v>
+        <v>126.7190849256571</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.01900703040852</v>
+        <v>18.95852991671016</v>
       </c>
       <c r="C6" t="n">
-        <v>284.8207169652676</v>
+        <v>254.4709684361818</v>
       </c>
       <c r="D6" t="n">
-        <v>77.52468921355364</v>
+        <v>82.39513957432206</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.95464398362217</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>251.6435350479509</v>
+        <v>289.7913055918692</v>
       </c>
       <c r="D7" t="n">
-        <v>43.35790561035613</v>
+        <v>43.83699849002857</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>162.6412334240478</v>
+        <v>156.2156946997524</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>70.88905648054941</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.23654444346124</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.148284961070273</v>
+        <v>0.9876381904722912</v>
       </c>
       <c r="C2" t="n">
-        <v>5.345616249623882</v>
+        <v>7.251188543566941</v>
       </c>
       <c r="D2" t="n">
-        <v>9.176395791594937</v>
+        <v>25.04143869222339</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.98637870532756</v>
+        <v>2.208932334555323</v>
       </c>
       <c r="C3" t="n">
-        <v>15.60487975900305</v>
+        <v>20.31726873938774</v>
       </c>
       <c r="D3" t="n">
-        <v>48.75849973141784</v>
+        <v>47.47241023885451</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.38950146334128</v>
+        <v>6.024003913258428</v>
       </c>
       <c r="C4" t="n">
-        <v>57.91722406433633</v>
+        <v>36.32270156172349</v>
       </c>
       <c r="D4" t="n">
-        <v>125.585166327252</v>
+        <v>113.8051756239945</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.45927197026759</v>
+        <v>16.64062358698344</v>
       </c>
       <c r="C5" t="n">
-        <v>162.896487827152</v>
+        <v>97.24211010564659</v>
       </c>
       <c r="D5" t="n">
-        <v>143.5069706682775</v>
+        <v>140.0953973960199</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>80.22155015711964</v>
+        <v>22.62143060125501</v>
       </c>
       <c r="C6" t="n">
-        <v>294.5616176868045</v>
+        <v>221.5048622752782</v>
       </c>
       <c r="D6" t="n">
-        <v>95.55743104515906</v>
+        <v>101.7159343938993</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.05847256056086</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>317.2792595630757</v>
+        <v>331.4124995134127</v>
       </c>
       <c r="D7" t="n">
-        <v>52.04146405441917</v>
+        <v>55.27534099220816</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>232.3207767329652</v>
+        <v>267.7029639940203</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>119.9234273168606</v>
+        <v>121.6984271661388</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>50.96252332745193</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.282023633026093</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C2" t="n">
-        <v>5.609706382066275</v>
+        <v>5.887540982368122</v>
       </c>
       <c r="D2" t="n">
-        <v>5.229770020522759</v>
+        <v>9.547496423800231</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.645229225868407</v>
+        <v>1.520727193878309</v>
       </c>
       <c r="C2" t="n">
-        <v>3.035563901531138</v>
+        <v>10.18759592696915</v>
       </c>
       <c r="D2" t="n">
-        <v>6.754424205218055</v>
+        <v>24.41704715232242</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.2534551386117</v>
+        <v>2.748893571891069</v>
       </c>
       <c r="C3" t="n">
-        <v>19.53187057599029</v>
+        <v>24.15590226299277</v>
       </c>
       <c r="D3" t="n">
-        <v>52.98983233672159</v>
+        <v>55.30675691874407</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.44951124648735</v>
+        <v>5.079562621772998</v>
       </c>
       <c r="C4" t="n">
-        <v>85.90586936470865</v>
+        <v>43.32943492693298</v>
       </c>
       <c r="D4" t="n">
-        <v>129.3118806125729</v>
+        <v>110.7293600665893</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.22206457427158</v>
+        <v>13.52357462599982</v>
       </c>
       <c r="C5" t="n">
-        <v>245.3878386764903</v>
+        <v>82.85950623843081</v>
       </c>
       <c r="D5" t="n">
-        <v>133.2477071588984</v>
+        <v>147.9248353373882</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.72709950041517</v>
+        <v>22.70193391300324</v>
       </c>
       <c r="C6" t="n">
-        <v>269.6055910448507</v>
+        <v>190.4305839404581</v>
       </c>
       <c r="D6" t="n">
-        <v>76.63915278432302</v>
+        <v>117.7763450876729</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.144578954431539</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>163.3706719683032</v>
+        <v>330.4543137540679</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>68.80971484295469</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.169662426385451</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>88.37201959777664</v>
+        <v>347.4797824411161</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>38.82812170296133</v>
+        <v>212.2234194793287</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
+        <v>87.68970494332511</v>
+      </c>
+      <c r="D10" t="n">
         <v>22.91890015564179</v>
-      </c>
-      <c r="D10" t="n">
-        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.70345544005523</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.012443924985719</v>
+        <v>5.385867905498002</v>
       </c>
       <c r="C2" t="n">
-        <v>5.362305960596078</v>
+        <v>8.116108271008383</v>
       </c>
       <c r="D2" t="n">
-        <v>8.58440192593411</v>
+        <v>13.10927709480766</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.58310138306037</v>
+        <v>7.309111658117503</v>
       </c>
       <c r="C3" t="n">
-        <v>14.13225820263284</v>
+        <v>11.62389281828224</v>
       </c>
       <c r="D3" t="n">
-        <v>7.530004891573036</v>
+        <v>9.547496423800231</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39871984264622</v>
+        <v>11.67842796936103</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14623917620671</v>
+        <v>59.94926357605328</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576319981487791</v>
+        <v>0.7785618646240685</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.283766144256333</v>
+        <v>3.402737542919445</v>
       </c>
       <c r="C2" t="n">
-        <v>3.413536767666159</v>
+        <v>9.293223768400306</v>
       </c>
       <c r="D2" t="n">
-        <v>17.16389511334699</v>
+        <v>12.36707583039707</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.72178985126643</v>
+        <v>14.49550485320416</v>
       </c>
       <c r="C3" t="n">
-        <v>18.58939277991335</v>
+        <v>25.00511402716626</v>
       </c>
       <c r="D3" t="n">
-        <v>12.91979978788802</v>
+        <v>18.6826588118168</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.29272504678157</v>
+        <v>9.112582190818893</v>
       </c>
       <c r="C4" t="n">
-        <v>22.06674314835556</v>
+        <v>19.46314823669302</v>
       </c>
       <c r="D4" t="n">
-        <v>19.01645303126072</v>
+        <v>19.23341927389927</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44319237810863</v>
+        <v>13.63119810473631</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15675747786919</v>
+        <v>73.76883680210237</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25119839539129</v>
+        <v>1.603670365263095</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.038329218194631</v>
+        <v>2.495602664195392</v>
       </c>
       <c r="C2" t="n">
-        <v>6.200718500022854</v>
+        <v>6.723990026386404</v>
       </c>
       <c r="D2" t="n">
-        <v>25.32320028334223</v>
+        <v>18.90257029756809</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.52972715413255</v>
+        <v>13.003248342749</v>
       </c>
       <c r="C3" t="n">
-        <v>15.36926030998382</v>
+        <v>32.29949946972006</v>
       </c>
       <c r="D3" t="n">
-        <v>23.65030219530566</v>
+        <v>24.55351008321273</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.90978668886309</v>
+        <v>20.49692856926491</v>
       </c>
       <c r="C4" t="n">
-        <v>36.475854203586</v>
+        <v>46.59669128666636</v>
       </c>
       <c r="D4" t="n">
-        <v>21.22440361811179</v>
+        <v>24.3767954964483</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.47510913559323</v>
+        <v>8.737554567796614</v>
       </c>
       <c r="C5" t="n">
-        <v>25.50089661781091</v>
+        <v>23.90555659840983</v>
       </c>
       <c r="D5" t="n">
-        <v>29.30516897176729</v>
+        <v>27.02260555939346</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73882905491661</v>
+        <v>14.84501652726559</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1068572349913</v>
+        <v>87.42065288278626</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021648716474983</v>
+        <v>2.474169421210932</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.166938167450963</v>
+        <v>1.648354395430395</v>
       </c>
       <c r="C2" t="n">
-        <v>5.290638378186061</v>
+        <v>13.17996292951343</v>
       </c>
       <c r="D2" t="n">
-        <v>24.7626223442173</v>
+        <v>19.30312336090079</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.19316761802514</v>
+        <v>10.52924412804704</v>
       </c>
       <c r="C3" t="n">
-        <v>20.38108234016379</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="D3" t="n">
-        <v>37.63529824230147</v>
+        <v>33.9782880439821</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.70482240285375</v>
+        <v>23.4706423654285</v>
       </c>
       <c r="C4" t="n">
-        <v>37.2288546927433</v>
+        <v>67.15743345670731</v>
       </c>
       <c r="D4" t="n">
-        <v>27.91206897944107</v>
+        <v>30.97512181669111</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.25103397931348</v>
+        <v>20.39580855572749</v>
       </c>
       <c r="C5" t="n">
-        <v>48.52288028239862</v>
+        <v>59.98478472948013</v>
       </c>
       <c r="D5" t="n">
-        <v>30.11511082777092</v>
+        <v>29.99239236474006</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.81260936167588</v>
+        <v>8.493099389439159</v>
       </c>
       <c r="C6" t="n">
-        <v>27.12961605915636</v>
+        <v>25.76105975943631</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06703823619285</v>
+        <v>16.09168113002233</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8659161123057</v>
+        <v>101.6316702948779</v>
       </c>
       <c r="D21" t="n">
-        <v>6.88268123283537</v>
+        <v>3.387722343162595</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.94684675525043</v>
+        <v>2.316924582022473</v>
       </c>
       <c r="C2" t="n">
-        <v>5.020657759518188</v>
+        <v>8.848492058376502</v>
       </c>
       <c r="D2" t="n">
-        <v>28.42159603794516</v>
+        <v>29.79211583307371</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.52772260099505</v>
+        <v>7.849072895453249</v>
       </c>
       <c r="C3" t="n">
-        <v>19.23734626471625</v>
+        <v>41.82736093943536</v>
       </c>
       <c r="D3" t="n">
-        <v>45.23402547317179</v>
+        <v>41.09105016125025</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.6695772964921</v>
+        <v>21.76043786463055</v>
       </c>
       <c r="C4" t="n">
-        <v>37.33095645398497</v>
+        <v>69.60787572650736</v>
       </c>
       <c r="D4" t="n">
-        <v>34.53592073999429</v>
+        <v>40.18980576875168</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.45243112740432</v>
+        <v>28.2252464970958</v>
       </c>
       <c r="C5" t="n">
-        <v>44.32590884674349</v>
+        <v>95.25407100454679</v>
       </c>
       <c r="D5" t="n">
-        <v>27.14532402242431</v>
+        <v>34.45934441906305</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.67047692873834</v>
+        <v>18.11324514335366</v>
       </c>
       <c r="C6" t="n">
-        <v>35.90447703971436</v>
+        <v>62.39006660488482</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>36.06548366321083</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>19.58292145661112</v>
+        <v>27.90716024091983</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.062850794885268</v>
+        <v>17.3640409959925</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21422620204939</v>
+        <v>115.4708726233501</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297138096163951</v>
+        <v>4.341010248998125</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.93801102591221</v>
+        <v>3.232895190084747</v>
       </c>
       <c r="C2" t="n">
-        <v>7.032258805519903</v>
+        <v>7.761697349775283</v>
       </c>
       <c r="D2" t="n">
-        <v>21.30097993904305</v>
+        <v>35.87306111317845</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.622993186036</v>
+        <v>7.819620464325844</v>
       </c>
       <c r="C3" t="n">
-        <v>19.49750940634166</v>
+        <v>37.63038950378024</v>
       </c>
       <c r="D3" t="n">
-        <v>58.88031856220246</v>
+        <v>53.79486545420398</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.71986741358695</v>
+        <v>18.21240166148258</v>
       </c>
       <c r="C4" t="n">
-        <v>44.33768981919445</v>
+        <v>88.07553179109411</v>
       </c>
       <c r="D4" t="n">
-        <v>51.02535518052373</v>
+        <v>50.47655821384976</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.15915060574178</v>
+        <v>30.704159450319</v>
       </c>
       <c r="C5" t="n">
-        <v>59.73934780341843</v>
+        <v>111.2565585837698</v>
       </c>
       <c r="D5" t="n">
-        <v>34.21390749300135</v>
+        <v>40.05530633326987</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>27.57238427377167</v>
       </c>
       <c r="C6" t="n">
-        <v>56.63407981488576</v>
+        <v>106.7473913781642</v>
       </c>
       <c r="D6" t="n">
-        <v>32.40258297866598</v>
+        <v>38.88309957439917</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.85187926984575</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C7" t="n">
-        <v>38.5669768136317</v>
+        <v>58.38944471007905</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>23.44904391593506</v>
+        <v>31.12631096314512</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.288629761557833</v>
+        <v>17.76500941538868</v>
       </c>
       <c r="C21" t="n">
-        <v>76.53061249635725</v>
+        <v>128.7963182615679</v>
       </c>
       <c r="D21" t="n">
-        <v>6.377551041363104</v>
+        <v>5.329502824616603</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.896376711706344</v>
+        <v>2.839214360681776</v>
       </c>
       <c r="C2" t="n">
-        <v>7.883434065101888</v>
+        <v>4.781111319681966</v>
       </c>
       <c r="D2" t="n">
-        <v>17.18156657202343</v>
+        <v>28.04362317181014</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.08579726536375</v>
+        <v>11.36372967665683</v>
       </c>
       <c r="C3" t="n">
-        <v>24.3620692808846</v>
+        <v>54.64407721837746</v>
       </c>
       <c r="D3" t="n">
-        <v>62.25753066481148</v>
+        <v>60.31857894892403</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.54792269662352</v>
+        <v>14.74094177926586</v>
       </c>
       <c r="C4" t="n">
-        <v>47.06891193240908</v>
+        <v>110.4868683836403</v>
       </c>
       <c r="D4" t="n">
-        <v>68.57409539393547</v>
+        <v>48.19203130606743</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.3378697456437</v>
+        <v>15.51161372709961</v>
       </c>
       <c r="C5" t="n">
-        <v>72.69841749947632</v>
+        <v>63.76451339083034</v>
       </c>
       <c r="D5" t="n">
-        <v>45.43037501402116</v>
+        <v>35.14656781203582</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.10323204432872</v>
+        <v>9.137125883425066</v>
       </c>
       <c r="C6" t="n">
-        <v>77.645444181176</v>
+        <v>38.44033135978387</v>
       </c>
       <c r="D6" t="n">
-        <v>36.26674194258143</v>
+        <v>25.43904651244335</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.70942804173872</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>63.12048689684442</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>39.13737222979909</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>27.17968519207294</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.503160985540522</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.286351333716</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.503160985540522</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
